--- a/docs/xlsx/jobs-2026-08-15.xlsx
+++ b/docs/xlsx/jobs-2026-08-15.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="55">
   <si>
     <t>Title</t>
   </si>
@@ -40,6 +40,45 @@
     <t>Link</t>
   </si>
   <si>
+    <t>Administrative Coordinator</t>
+  </si>
+  <si>
+    <t>Lutheran Settlement House</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 45000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Housing Homelessness, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cc1c9d9b6597406ab0ee111b4632f8ad-administrative-coordinator-lutheran-settlement-house-philadelphia</t>
+  </si>
+  <si>
+    <t>Case Manager</t>
+  </si>
+  <si>
+    <t>SAG-AFTRA Foundation</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 70.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Disaster Relief, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/57f51b63bbe544e88f69cb3f830f254a-case-manager-sag-aftra-foundation-los-angeles</t>
+  </si>
+  <si>
     <t>Cross-Borough Operations Administrator</t>
   </si>
   <si>
@@ -49,9 +88,6 @@
     <t>New York, New York</t>
   </si>
   <si>
-    <t>Full Time</t>
-  </si>
-  <si>
     <t>USD 72500.00 - 75000.00/year</t>
   </si>
   <si>
@@ -79,16 +115,31 @@
     <t>https://www.idealist.org/en/nonprofit-job/a0c905e95b6d4343acef7aa0b755adc1-executrive-director-diocese-of-norwich-ct-outreach-to-haiti-norwich</t>
   </si>
   <si>
+    <t>Freelancer International Fundraiser</t>
+  </si>
+  <si>
+    <t>Swift Sports Organisation</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>USD 50.00 - 100.00/month</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e1a14cf1495143cb925583f8cf5ced16-freelancer-international-fundraiser-swift-sports-organisation-kampala</t>
+  </si>
+  <si>
     <t>P/T Nonprofit Project Manager &amp; Grant Write</t>
   </si>
   <si>
     <t>THE MARY N. BASSIOUNI FOUNDATION</t>
-  </si>
-  <si>
-    <t>Remote</t>
-  </si>
-  <si>
-    <t>Contract</t>
   </si>
   <si>
     <t>Children Youth, Women, Economic Development</t>
@@ -609,7 +660,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -705,10 +756,10 @@
         <v>23</v>
       </c>
       <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
         <v>24</v>
-      </c>
-      <c r="E4" t="s">
-        <v>18</v>
       </c>
       <c r="F4" t="s">
         <v>25</v>
@@ -748,19 +799,88 @@
         <v>34</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" t="s">
         <v>35</v>
       </c>
-      <c r="F6" t="s">
+      <c r="D7" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>37</v>
+      <c r="E7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -771,6 +891,9 @@
     <hyperlink ref="H4" r:id="rId3"/>
     <hyperlink ref="H5" r:id="rId4"/>
     <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/docs/xlsx/jobs-2026-08-15.xlsx
+++ b/docs/xlsx/jobs-2026-08-15.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="61">
   <si>
     <t>Title</t>
   </si>
@@ -179,6 +179,24 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/79621b964b5c40508261b5eb34a8b7b7-quality-assurance-qa-contractor-the-19th-austin</t>
+  </si>
+  <si>
+    <t>Vegan rescue and sanctuary director/development officer</t>
+  </si>
+  <si>
+    <t>Vietnam Animal Aid and Rescue-US</t>
+  </si>
+  <si>
+    <t>Da Nang, Da Nang, VN</t>
+  </si>
+  <si>
+    <t>USD 800.00 - 1200.00/month</t>
+  </si>
+  <si>
+    <t>Education, Environment, Animals</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8b798aef0c714f6f85d3363e09433775-vegan-rescue-and-sanctuary-directordevelopment-officer-vietnam-animal-aid-and-rescue-us-da-nang</t>
   </si>
 </sst>
 </file>
@@ -660,7 +678,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -883,6 +901,29 @@
         <v>54</v>
       </c>
     </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" t="s">
+        <v>59</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <hyperlinks>
@@ -894,6 +935,7 @@
     <hyperlink ref="H7" r:id="rId6"/>
     <hyperlink ref="H8" r:id="rId7"/>
     <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
